--- a/docs/kanji_n4.xlsx
+++ b/docs/kanji_n4.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IG24-253\Documents\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DCB4AC-58EF-4419-AA53-E764F6EA603B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6850"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JLPT N4 Kanji" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Kanji</t>
   </si>
@@ -172,23 +173,104 @@
   <si>
     <t>n4_close.webp</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>春</t>
+  </si>
+  <si>
+    <t>旅行</t>
+  </si>
+  <si>
+    <t>四季</t>
+  </si>
+  <si>
+    <t>外国</t>
+  </si>
+  <si>
+    <t>池</t>
+  </si>
+  <si>
+    <t>学校</t>
+  </si>
+  <si>
+    <t>先生</t>
+  </si>
+  <si>
+    <t>映画</t>
+  </si>
+  <si>
+    <t>音楽</t>
+  </si>
+  <si>
+    <t>はる</t>
+  </si>
+  <si>
+    <t>りょこう</t>
+  </si>
+  <si>
+    <t>しき</t>
+  </si>
+  <si>
+    <t>がいこく</t>
+  </si>
+  <si>
+    <t>いけ</t>
+  </si>
+  <si>
+    <t>がっこう</t>
+  </si>
+  <si>
+    <t>せんせい</t>
+  </si>
+  <si>
+    <t>えいが</t>
+  </si>
+  <si>
+    <t>おんがく</t>
+  </si>
+  <si>
+    <t>spring</t>
+  </si>
+  <si>
+    <t>trip/travel</t>
+  </si>
+  <si>
+    <t>four seasons</t>
+  </si>
+  <si>
+    <t>foreign country</t>
+  </si>
+  <si>
+    <t>pond</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>teacher</t>
+  </si>
+  <si>
+    <t>movie</t>
+  </si>
+  <si>
+    <t>music</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -218,7 +300,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -517,11 +599,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -535,7 +617,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -549,7 +631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -563,7 +645,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -577,7 +659,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -591,7 +673,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -605,7 +687,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -619,7 +701,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -633,7 +715,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -647,7 +729,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -661,7 +743,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -673,6 +755,105 @@
       </c>
       <c r="D11" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/docs/kanji_n4.xlsx
+++ b/docs/kanji_n4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\temp_kanjis_to_add\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DCB4AC-58EF-4419-AA53-E764F6EA603B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83A00CA-F29E-400A-99C1-D89908259CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Kanji</t>
   </si>
@@ -254,6 +254,15 @@
   </si>
   <si>
     <t>music</t>
+  </si>
+  <si>
+    <t>坊門</t>
+  </si>
+  <si>
+    <t>ぼうもん</t>
+  </si>
+  <si>
+    <t>temple gate</t>
   </si>
 </sst>
 </file>
@@ -600,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -854,6 +863,17 @@
       </c>
       <c r="C20" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/docs/kanji_n4.xlsx
+++ b/docs/kanji_n4.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JLPT N4 Kanji" sheetId="1" r:id="Rf24048eb9be3401e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JLPT N4 Kanji" sheetId="1" r:id="R07ac2e330afe494f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -787,7 +787,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2" t="str">
-        <x:v>無し</x:v>
+        <x:v>無</x:v>
       </x:c>
       <x:c r="B24" s="2" t="str">
         <x:v>なし</x:v>
